--- a/abidjan_2026/schedule.xlsx
+++ b/abidjan_2026/schedule.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/127527/Dropbox/LDID 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WZB Dropbox\Macartan Humphreys\LDID 2026\Slides_abidjan_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB48A0B-3052-9648-934F-A87B8064AEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D424FA82-8E46-44A3-A95F-CE5C36354017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="600" windowWidth="36000" windowHeight="21000" xr2:uid="{A7CADD52-3E9C-8F4C-9C8E-F3DB24500964}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A7CADD52-3E9C-8F4C-9C8E-F3DB24500964}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="138">
   <si>
     <t>Day</t>
   </si>
@@ -293,12 +293,6 @@
     <t>Brice and Vin</t>
   </si>
   <si>
-    <t>Macartan</t>
-  </si>
-  <si>
-    <t>Macartan, Adikath</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
@@ -453,6 +447,12 @@
   </si>
   <si>
     <t>Fr: Yannick and Alyssa</t>
+  </si>
+  <si>
+    <t>Macartan, Alyssa</t>
+  </si>
+  <si>
+    <t>Macartan, ALyssa</t>
   </si>
 </sst>
 </file>
@@ -826,14 +826,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF77D7AD-A533-3D4F-907F-890927E36104}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="43.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="3" width="43.375" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -855,7 +855,7 @@
         <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>83</v>
@@ -864,7 +864,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -875,13 +875,13 @@
         <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>43</v>
       </c>
@@ -892,7 +892,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>44</v>
       </c>
@@ -900,21 +900,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>10</v>
       </c>
@@ -933,13 +933,13 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>46</v>
       </c>
@@ -950,10 +950,10 @@
         <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>55</v>
       </c>
@@ -961,16 +961,16 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>56</v>
       </c>
@@ -978,7 +978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>57</v>
       </c>
@@ -986,24 +986,24 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>58</v>
       </c>
@@ -1011,13 +1011,13 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>0.79166666666666663</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>18</v>
       </c>
@@ -1044,13 +1044,13 @@
         <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>20</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>21</v>
       </c>
@@ -1066,21 +1066,21 @@
         <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>22</v>
       </c>
@@ -1091,13 +1091,13 @@
         <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F23" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>64</v>
       </c>
@@ -1113,24 +1113,24 @@
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>65</v>
       </c>
@@ -1141,13 +1141,13 @@
         <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>66</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>67</v>
       </c>
@@ -1166,18 +1166,21 @@
         <v>63</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>58</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1188,106 +1191,106 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
         <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F34" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
         <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -1298,7 +1301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>32</v>
       </c>
@@ -1306,21 +1309,21 @@
         <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>33</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>34</v>
       </c>
@@ -1336,16 +1339,16 @@
         <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F49" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>22</v>
       </c>
@@ -1353,13 +1356,13 @@
         <v>76</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E50" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>8</v>
       </c>
@@ -1367,7 +1370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>72</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>80</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>81</v>
       </c>
@@ -1402,7 +1405,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>70</v>
       </c>
@@ -1410,13 +1413,13 @@
         <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>8</v>
       </c>
@@ -1424,7 +1427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="1">
         <v>0.625</v>
       </c>
